--- a/2026/CABRERA/Febrero/Febrero CABRERA.xlsx
+++ b/2026/CABRERA/Febrero/Febrero CABRERA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\CABRERA\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\CABRERA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD3E819-6751-4FF3-9604-3D38B3BE49C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2881B9-4BBD-4272-9A9C-74FF9F32A4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$98</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="134">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -196,9 +201,6 @@
     <t>Punitorios mal cobrados</t>
   </si>
   <si>
-    <t>PREVISION ORDINARIA</t>
-  </si>
-  <si>
     <t>SI EN LA COLUMNA LLAMADA DEUDA O SALDO A FAVOR FIGURA UN NUMERO EN NEGATIVO SIGNIFICA QUE LA UF POSEE DINERO A FAVOR (ES DECIR PAGO DE MAS)</t>
   </si>
   <si>
@@ -328,9 +330,6 @@
     <t>Ascensores Guillemi - Mantenimiento de ascensores</t>
   </si>
   <si>
-    <t xml:space="preserve">Honorarios administracion </t>
-  </si>
-  <si>
     <t>Banco Santander  - Gastos bancarios</t>
   </si>
   <si>
@@ -349,28 +348,10 @@
     <t>TELEFONO : 11-5320-2676 - MAIL: cabrera140rc@gmail.com - OFICINA CON CITA PREVIA - DR MELO 2958 8° PISO</t>
   </si>
   <si>
-    <t>Transf 30/01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Servisur - cambio de 5 plafones, 6 lamparas, 3 sensores </t>
-  </si>
-  <si>
-    <t>Casa Ruan - compra de materiales electricos</t>
-  </si>
-  <si>
     <t xml:space="preserve">AySA </t>
   </si>
   <si>
     <t xml:space="preserve">Salvati Leonel Amilcar - Servicio de limpieza </t>
-  </si>
-  <si>
-    <t>Transf 22/01</t>
-  </si>
-  <si>
-    <t>Se transfieren mes proximo</t>
-  </si>
-  <si>
-    <t>Transf 02/01</t>
   </si>
   <si>
     <t>Lucia de dominicis</t>
@@ -400,18 +381,6 @@
     <t>EXTRAORDINARIOS:</t>
   </si>
   <si>
-    <t>Transferencia 10/01 - Sr Franco Attolino</t>
-  </si>
-  <si>
-    <t>Transferencia 13/01 - Sr Facundo Guariniello</t>
-  </si>
-  <si>
-    <t>Transferencia 14/01 - Sra Silvia Marin De Sarni</t>
-  </si>
-  <si>
-    <t>Transferencia 20/01 - Sra Melisa Belmonte</t>
-  </si>
-  <si>
     <t>Saldo anterior REAL según banco</t>
   </si>
   <si>
@@ -437,6 +406,36 @@
   </si>
   <si>
     <t>Transf 02/02</t>
+  </si>
+  <si>
+    <t>Debito 02/02</t>
+  </si>
+  <si>
+    <t>Transf 06/02</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Mes anterior - Se adeuda Febrero</t>
+  </si>
+  <si>
+    <t>Falta presentar documentacion</t>
+  </si>
+  <si>
+    <t>Transferencia ya identificada mes anterior</t>
+  </si>
+  <si>
+    <t>Transferencia 11/02 - Sra Silvia Marin De Sarni</t>
+  </si>
+  <si>
+    <t>Facundo Guarinello</t>
+  </si>
+  <si>
+    <t>Transferencia 24/02 - Sr De Rivero Lucas Damian</t>
+  </si>
+  <si>
+    <t>No se debito</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA - LIMPIEZA DE TANQUE</t>
   </si>
 </sst>
 </file>
@@ -450,7 +449,7 @@
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -624,13 +623,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1071,7 +1063,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1287,21 +1279,7 @@
     <xf numFmtId="44" fontId="0" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1331,6 +1309,54 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1340,9 +1366,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1352,9 +1375,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1370,50 +1390,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1482,9 +1458,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1522,9 +1498,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1557,9 +1533,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1592,9 +1585,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1768,21 +1778,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L97"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L98"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.28515625" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="100" t="s">
         <v>50</v>
       </c>
@@ -1790,102 +1800,102 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="96" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B2" s="96"/>
       <c r="C2" s="96"/>
       <c r="D2" s="96"/>
     </row>
-    <row r="3" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="96" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" s="96"/>
       <c r="C3" s="96"/>
       <c r="D3" s="96"/>
     </row>
-    <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="148" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="148"/>
+    <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="142" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="142"/>
       <c r="C4" s="97"/>
       <c r="D4" s="97"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="142"/>
+      <c r="B5" s="142"/>
       <c r="C5" s="97"/>
       <c r="D5" s="97"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="148"/>
-      <c r="B6" s="148"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="142"/>
+      <c r="B6" s="142"/>
       <c r="C6" s="97"/>
       <c r="D6" s="97"/>
     </row>
-    <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="148"/>
-      <c r="B7" s="148"/>
+    <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="142"/>
+      <c r="B7" s="142"/>
       <c r="C7" s="97"/>
       <c r="D7" s="97"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="156" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="156"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="156"/>
-    </row>
-    <row r="13" spans="1:8" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="150" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="150"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="150"/>
+    </row>
+    <row r="13" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" t="s">
         <v>103</v>
       </c>
-      <c r="G13" t="s">
-        <v>104</v>
-      </c>
-      <c r="H13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="149" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="143" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="149"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="149"/>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="149"/>
-      <c r="B15" s="149"/>
-      <c r="C15" s="149"/>
-      <c r="D15" s="149"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="149"/>
-      <c r="B16" s="149"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="149"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="149"/>
-      <c r="B17" s="149"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="149"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="143"/>
+      <c r="C14" s="143"/>
+      <c r="D14" s="143"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="143"/>
+      <c r="B15" s="143"/>
+      <c r="C15" s="143"/>
+      <c r="D15" s="143"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="143"/>
+      <c r="B16" s="143"/>
+      <c r="C16" s="143"/>
+      <c r="D16" s="143"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="143"/>
+      <c r="B17" s="143"/>
+      <c r="C17" s="143"/>
+      <c r="D17" s="143"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>15</v>
       </c>
@@ -1893,7 +1903,7 @@
       <c r="C21" s="8"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
         <v>40</v>
       </c>
@@ -1901,43 +1911,43 @@
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="112">
-        <v>250000</v>
+        <v>395000</v>
       </c>
       <c r="D23" s="105" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="112"/>
       <c r="D24" s="99"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="112"/>
       <c r="D25" s="99"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="112"/>
       <c r="D26" s="99"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="113"/>
       <c r="D27" s="99"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
         <v>41</v>
       </c>
@@ -1948,7 +1958,7 @@
       </c>
       <c r="D28" s="69"/>
     </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>0</v>
       </c>
@@ -1956,12 +1966,12 @@
       <c r="C29" s="18"/>
       <c r="D29" s="70">
         <f>C23+C28</f>
-        <v>250000</v>
+        <v>395000</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
         <v>26</v>
       </c>
@@ -1970,18 +1980,18 @@
       <c r="D30" s="71"/>
       <c r="F30" s="13"/>
     </row>
-    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="101" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B31" s="94"/>
-      <c r="C31" s="132" t="s">
-        <v>113</v>
+      <c r="C31" s="132">
+        <v>102000</v>
       </c>
       <c r="D31" s="110"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>22</v>
       </c>
@@ -1989,10 +1999,10 @@
       <c r="C32" s="27"/>
       <c r="D32" s="70">
         <f>SUM(C31:C31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+        <v>102000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
         <v>37</v>
       </c>
@@ -2000,19 +2010,17 @@
       <c r="C33" s="25"/>
       <c r="D33" s="50"/>
     </row>
-    <row r="34" spans="1:6" s="30" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="154" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="155"/>
-      <c r="C34" s="134">
-        <v>129795.05</v>
-      </c>
-      <c r="D34" s="109" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" s="30" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="149"/>
+      <c r="C34" s="134" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="109"/>
+    </row>
+    <row r="35" spans="1:6" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>1</v>
       </c>
@@ -2020,10 +2028,10 @@
       <c r="C35" s="27"/>
       <c r="D35" s="72">
         <f>SUM(C34:C34)</f>
-        <v>129795.05</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23" t="s">
         <v>23</v>
       </c>
@@ -2031,48 +2039,48 @@
       <c r="C36" s="28"/>
       <c r="D36" s="73"/>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C37" s="135"/>
       <c r="D37" s="109"/>
       <c r="F37" s="102"/>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C38" s="114"/>
       <c r="D38" s="109"/>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C39" s="114"/>
       <c r="D39" s="109"/>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C40" s="114"/>
       <c r="D40" s="108"/>
     </row>
-    <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>2</v>
       </c>
@@ -2083,7 +2091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
         <v>25</v>
       </c>
@@ -2091,43 +2099,43 @@
       <c r="C42" s="28"/>
       <c r="D42" s="73"/>
     </row>
-    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B43" s="5"/>
-      <c r="C43" s="184">
+      <c r="C43" s="114">
         <v>84708.24</v>
       </c>
       <c r="D43" s="107" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="114">
-        <v>183437.9</v>
+        <v>185724.36</v>
       </c>
       <c r="D44" s="105" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B45" s="5"/>
-      <c r="C45" s="185">
-        <v>252083.88</v>
+      <c r="C45" s="114">
+        <v>259590</v>
       </c>
       <c r="D45" s="105" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="16" t="s">
         <v>3</v>
       </c>
@@ -2135,10 +2143,10 @@
       <c r="C46" s="27"/>
       <c r="D46" s="72">
         <f>SUM(C43:C45)</f>
-        <v>520230.02</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>530022.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
         <v>24</v>
       </c>
@@ -2146,362 +2154,366 @@
       <c r="C47" s="27"/>
       <c r="D47" s="75"/>
     </row>
-    <row r="48" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="126" t="s">
+        <v>98</v>
+      </c>
+      <c r="B48" s="104"/>
+      <c r="C48" s="114" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="105"/>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="23"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="78">
+        <f>SUM(C48:C48)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="49"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="75"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="114">
+        <v>57500</v>
+      </c>
+      <c r="D51" s="79"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B48" s="104"/>
-      <c r="C48" s="114">
-        <v>60000</v>
-      </c>
-      <c r="D48" s="105" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="126" t="s">
-        <v>109</v>
-      </c>
-      <c r="B49" s="104"/>
-      <c r="C49" s="114">
-        <v>130200</v>
-      </c>
-      <c r="D49" s="105" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="126" t="s">
-        <v>108</v>
-      </c>
-      <c r="B50" s="104"/>
-      <c r="C50" s="114">
-        <v>155000</v>
-      </c>
-      <c r="D50" s="105" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" s="23"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="78">
-        <f>SUM(C48:C50)</f>
-        <v>345200</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B52" s="49"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="75"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="114">
-        <v>57500</v>
-      </c>
-      <c r="D53" s="79"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>101</v>
-      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="114">
+        <f>4684.8+33979.94</f>
+        <v>38664.740000000005</v>
+      </c>
+      <c r="D52" s="77"/>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="39"/>
+      <c r="C53" s="80"/>
+      <c r="D53" s="72">
+        <f>SUM(C51:C52)</f>
+        <v>96164.74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="114">
-        <v>32008</v>
-      </c>
-      <c r="D54" s="77"/>
-    </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="B55" s="39"/>
-      <c r="C55" s="80"/>
-      <c r="D55" s="72">
-        <f>SUM(C53:C54)</f>
-        <v>89508</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="68"/>
-      <c r="D56" s="81"/>
-    </row>
-    <row r="57" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="150" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="151"/>
-      <c r="C57" s="152"/>
-      <c r="D57" s="82"/>
-    </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="1"/>
+      <c r="C54" s="68"/>
+      <c r="D54" s="81"/>
+    </row>
+    <row r="55" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="144" t="s">
+        <v>133</v>
+      </c>
+      <c r="B55" s="145"/>
+      <c r="C55" s="146"/>
+      <c r="D55" s="82">
+        <f>1350000-1123187.34</f>
+        <v>226812.65999999992</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1"/>
+      <c r="C56" s="83"/>
+      <c r="D56" s="84"/>
+      <c r="E56" s="34"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="85"/>
+      <c r="D57" s="86">
+        <f>(SUM(D24:D55))</f>
+        <v>1350000</v>
+      </c>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C58" s="83"/>
-      <c r="D58" s="84"/>
-      <c r="E58" s="34"/>
-    </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="85"/>
-      <c r="D59" s="86">
-        <f>(SUM(D24:D57))</f>
-        <v>1334733.07</v>
-      </c>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C60" s="83"/>
-      <c r="D60" s="83"/>
-      <c r="F60" s="103"/>
-    </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C61" s="83"/>
-      <c r="D61" s="83"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="10" t="s">
+      <c r="D58" s="83"/>
+      <c r="F58" s="103"/>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C59" s="83"/>
+      <c r="D59" s="83"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B62" s="11"/>
-      <c r="C62" s="87"/>
-      <c r="D62" s="88"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="154"/>
-      <c r="B63" s="155"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="87"/>
+      <c r="D60" s="88"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="148"/>
+      <c r="B61" s="149"/>
+      <c r="C61" s="76"/>
+      <c r="D61" s="74"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="148"/>
+      <c r="B62" s="149"/>
+      <c r="C62" s="76"/>
+      <c r="D62" s="74"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="91"/>
+      <c r="B63" s="92"/>
       <c r="C63" s="76"/>
       <c r="D63" s="74"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="154"/>
-      <c r="B64" s="155"/>
-      <c r="C64" s="76"/>
-      <c r="D64" s="74"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="91"/>
-      <c r="B65" s="92"/>
-      <c r="C65" s="76"/>
-      <c r="D65" s="74"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="37"/>
-      <c r="B66" s="36"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="43">
-        <f>SUM(C63:C65)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="19" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="37"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43">
+        <f>SUM(C61:C63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B69" s="19"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="111"/>
-    </row>
-    <row r="70" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
+      <c r="B67" s="19"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="111"/>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="51">
-        <f>D66+D69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B69" s="9"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="51">
+        <f>D64+D67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="B71" s="67">
+        <f>D57</f>
+        <v>1350000</v>
+      </c>
+      <c r="C71" s="34"/>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="B72" s="67">
+        <f>D57-D55</f>
+        <v>1123187.3400000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="66" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B73" s="67">
-        <f>D59</f>
-        <v>1334733.07</v>
-      </c>
-      <c r="C73" s="34"/>
-    </row>
-    <row r="74" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>D69-D67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="66" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B74" s="67">
-        <f>D59-D57</f>
-        <v>1334733.07</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="66" t="s">
-        <v>30</v>
-      </c>
-      <c r="B75" s="67">
-        <f>D71-D69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="66" t="s">
-        <v>45</v>
-      </c>
-      <c r="B76" s="67">
-        <f>D71</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="14" t="s">
+        <f>D69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B80" s="31"/>
-    </row>
-    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="127" t="s">
-        <v>127</v>
-      </c>
-      <c r="B81" s="93">
-        <v>397838</v>
-      </c>
-      <c r="D81" s="34"/>
-    </row>
-    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="128" t="s">
+      <c r="B78" s="31"/>
+    </row>
+    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="127" t="s">
+        <v>115</v>
+      </c>
+      <c r="B79" s="93">
+        <v>532845.39999999991</v>
+      </c>
+      <c r="D79" s="34"/>
+    </row>
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="128" t="s">
         <v>48</v>
       </c>
-      <c r="B82" s="32">
+      <c r="B80" s="32">
         <f>PRORRATEO!G18</f>
-        <v>914085.10000000009</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="128" t="s">
+        <v>1685206.5899999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="128" t="s">
         <v>47</v>
       </c>
-      <c r="B83" s="77">
-        <f>B96</f>
-        <v>470947.13</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="77">
+        <f>B97</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B82" s="106">
+        <v>-2372</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B83" s="106">
+        <v>-2997</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B84" s="106"/>
-    </row>
-    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="106">
+        <v>-15817</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B85" s="106">
+        <v>-119447.13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B86" s="106">
+        <v>-80500</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B87" s="106">
+        <v>-185000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B85" s="106">
-        <f>-B74</f>
-        <v>-1334733.07</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="15" t="s">
+      <c r="B88" s="106">
+        <f>-B72</f>
+        <v>-1123187.3400000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B86" s="77">
-        <f>-(B75)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="129" t="s">
+      <c r="B89" s="77">
+        <f>-(B73)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="B87" s="93">
-        <f>SUM(B81:B86)</f>
-        <v>448137.15999999992</v>
-      </c>
-      <c r="D87" s="34"/>
-    </row>
-    <row r="88" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="33"/>
-      <c r="C88" s="34"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="153" t="s">
+      <c r="B90" s="93">
+        <f>SUM(B79:B89)</f>
+        <v>888731.51999999979</v>
+      </c>
+      <c r="D90" s="34"/>
+    </row>
+    <row r="91" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="33"/>
+      <c r="C91" s="34"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="B90" s="153"/>
-    </row>
-    <row r="91" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="153"/>
-      <c r="B91" s="153"/>
-    </row>
-    <row r="92" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="89" t="s">
-        <v>123</v>
-      </c>
-      <c r="B92" s="26">
-        <v>80500</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="89" t="s">
-        <v>124</v>
-      </c>
-      <c r="B93" s="26">
-        <v>185000</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="89" t="s">
-        <v>125</v>
-      </c>
-      <c r="B94" s="26">
-        <v>86000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B93" s="147"/>
+    </row>
+    <row r="94" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="147"/>
+      <c r="B94" s="147"/>
+    </row>
+    <row r="95" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="89" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B95" s="26">
-        <v>119447.13</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="35" t="s">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="89" t="s">
+        <v>131</v>
+      </c>
+      <c r="B96" s="26">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B96" s="90">
-        <f>SUM(B92:B95)</f>
-        <v>470947.13</v>
-      </c>
-    </row>
-    <row r="97" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L97" s="7"/>
+      <c r="B97" s="90">
+        <f>SUM(B95:B96)</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L98" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A90:B91"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A93:B94"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
@@ -2514,52 +2526,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" customWidth="1"/>
-    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="174" t="str">
+      <c r="B1" s="155" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco: Santander
 C.U.I.T.   30-71774143-5
 CBU: 0720533020000000956840 ALIAS: BLONDA.LAGO.CORO
 Nº de cuenta: 533-009568/4</v>
       </c>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="174" t="s">
-        <v>128</v>
-      </c>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="170" t="s">
-        <v>120</v>
-      </c>
-      <c r="K1" s="171"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="155" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="151" t="s">
+        <v>112</v>
+      </c>
+      <c r="K1" s="152"/>
       <c r="L1" s="136" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="M1" s="136"/>
       <c r="N1" s="138">
@@ -2568,123 +2580,121 @@
       <c r="O1" s="130"/>
       <c r="P1" s="13"/>
     </row>
-    <row r="2" spans="1:18" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="177"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="178"/>
-      <c r="H2" s="178"/>
-      <c r="I2" s="179"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="173"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="153"/>
+      <c r="K2" s="154"/>
       <c r="L2" s="137" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="M2" s="137"/>
       <c r="N2" s="115"/>
       <c r="O2" s="131"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="180" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="161" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="182" t="s">
+      <c r="B3" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="165" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="160" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="160" t="s">
+      <c r="D3" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="160" t="s">
+      <c r="E3" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="160" t="s">
+      <c r="F3" s="165" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="160" t="s">
+      <c r="G3" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="160" t="s">
+      <c r="H3" s="165" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="165" t="s">
+      <c r="I3" s="173" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="162" t="s">
+      <c r="J3" s="171" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="162" t="s">
+      <c r="K3" s="171" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="162" t="s">
+      <c r="L3" s="171" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="168" t="s">
+      <c r="M3" s="176" t="s">
         <v>44</v>
       </c>
       <c r="N3" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="157" t="s">
+      <c r="O3" s="167" t="s">
         <v>42</v>
       </c>
       <c r="R3" s="34"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="181"/>
-      <c r="B4" s="183"/>
-      <c r="C4" s="164"/>
-      <c r="D4" s="164"/>
-      <c r="E4" s="161"/>
-      <c r="F4" s="164"/>
-      <c r="G4" s="164"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="166"/>
-      <c r="J4" s="163"/>
-      <c r="K4" s="167"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="169"/>
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="162"/>
+      <c r="B4" s="164"/>
+      <c r="C4" s="166"/>
+      <c r="D4" s="166"/>
+      <c r="E4" s="170"/>
+      <c r="F4" s="166"/>
+      <c r="G4" s="166"/>
+      <c r="H4" s="170"/>
+      <c r="I4" s="174"/>
+      <c r="J4" s="172"/>
+      <c r="K4" s="175"/>
+      <c r="L4" s="172"/>
+      <c r="M4" s="177"/>
       <c r="N4" s="44" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="O4" s="158"/>
-    </row>
-    <row r="5" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O4" s="168"/>
+    </row>
+    <row r="5" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="D5" s="122" t="s">
         <v>62</v>
-      </c>
-      <c r="D5" s="122" t="s">
-        <v>63</v>
       </c>
       <c r="E5" s="48">
         <v>6.84</v>
       </c>
       <c r="F5" s="53">
-        <v>361209.25</v>
-      </c>
-      <c r="G5" s="54">
-        <v>300000</v>
-      </c>
+        <v>148515.01</v>
+      </c>
+      <c r="G5" s="54"/>
       <c r="H5" s="55"/>
       <c r="I5" s="56">
         <f>F5-G5</f>
-        <v>61209.25</v>
+        <v>148515.01</v>
       </c>
       <c r="J5" s="56">
         <f>IF(I5&gt;0,I5*2.95%,0)</f>
-        <v>1805.6728750000002</v>
+        <v>4381.1927950000008</v>
       </c>
       <c r="K5" s="57">
         <f t="shared" ref="K5:K16" si="0">N$2*E5%</f>
@@ -2699,39 +2709,39 @@
       </c>
       <c r="N5" s="59">
         <f>ROUND(I5+J5+K5+L5+M5,0) + P5</f>
-        <v>148515.01</v>
+        <v>238396.01</v>
       </c>
       <c r="O5" s="60">
         <f t="shared" ref="O5:O16" si="2">ROUND(N5*3%,0) + N5</f>
-        <v>152970.01</v>
+        <v>245548.01</v>
       </c>
       <c r="P5" s="34">
         <v>0.01</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
-    <row r="6" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="123" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="123" t="s">
+      <c r="D6" s="116" t="s">
         <v>65</v>
-      </c>
-      <c r="D6" s="116" t="s">
-        <v>66</v>
       </c>
       <c r="E6" s="124">
         <v>7.79</v>
       </c>
       <c r="F6" s="53">
-        <v>84570.14</v>
+        <v>97375.02</v>
       </c>
       <c r="G6" s="54">
         <f t="shared" ref="G6:G16" si="3">F6</f>
-        <v>84570.14</v>
+        <v>97375.02</v>
       </c>
       <c r="H6" s="55"/>
       <c r="I6" s="117">
@@ -2766,32 +2776,33 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="147" t="s">
+    <row r="7" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="141" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="123" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="123" t="s">
+      <c r="D7" s="123" t="s">
         <v>68</v>
-      </c>
-      <c r="D7" s="123" t="s">
-        <v>69</v>
       </c>
       <c r="E7" s="124">
         <v>6.75</v>
       </c>
       <c r="F7" s="54">
-        <v>73279.649999999994</v>
+        <v>84375.03</v>
       </c>
       <c r="G7" s="54">
-        <v>73280</v>
+        <f>F7</f>
+        <v>84375.03</v>
       </c>
       <c r="H7" s="55"/>
       <c r="I7" s="56">
         <f t="shared" si="4"/>
-        <v>-0.35000000000582077</v>
+        <v>0</v>
       </c>
       <c r="J7" s="56">
         <f t="shared" si="5"/>
@@ -2821,36 +2832,37 @@
         <v>0.03</v>
       </c>
       <c r="Q7" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="R7" s="34"/>
     </row>
-    <row r="8" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="143" t="s">
+      <c r="B8" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="143" t="s">
+      <c r="D8" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="143" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="144">
+      <c r="E8" s="124">
         <v>7.41</v>
       </c>
-      <c r="F8" s="145">
-        <v>80426.179999999993</v>
+      <c r="F8" s="54">
+        <v>175424.04</v>
       </c>
       <c r="G8" s="54">
-        <v>80500</v>
+        <f>92552.04+80500+2372</f>
+        <v>175424.03999999998</v>
       </c>
       <c r="H8" s="55"/>
       <c r="I8" s="56">
         <f t="shared" si="4"/>
-        <v>-73.820000000006985</v>
+        <v>0</v>
       </c>
       <c r="J8" s="56">
         <f t="shared" si="5"/>
@@ -2869,49 +2881,49 @@
       </c>
       <c r="N8" s="59">
         <f t="shared" si="6"/>
-        <v>92551.039999999994</v>
+        <v>92625.04</v>
       </c>
       <c r="O8" s="60">
         <f t="shared" si="2"/>
-        <v>95328.04</v>
+        <v>95404.04</v>
       </c>
       <c r="P8" s="34">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
       <c r="Q8" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="R8" s="34"/>
     </row>
-    <row r="9" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="122" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="122" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="122" t="s">
+      <c r="D9" s="122" t="s">
         <v>74</v>
-      </c>
-      <c r="D9" s="122" t="s">
-        <v>75</v>
       </c>
       <c r="E9" s="133">
         <v>8</v>
       </c>
       <c r="F9" s="53">
-        <v>85093.2</v>
+        <v>187603.05</v>
       </c>
       <c r="G9" s="54"/>
       <c r="H9" s="55"/>
       <c r="I9" s="56">
         <f t="shared" si="4"/>
-        <v>85093.2</v>
+        <v>187603.05</v>
       </c>
       <c r="J9" s="56">
         <f t="shared" si="5"/>
-        <v>2510.2494000000002</v>
+        <v>5534.2899749999997</v>
       </c>
       <c r="K9" s="57">
         <f t="shared" si="0"/>
@@ -2926,45 +2938,47 @@
       </c>
       <c r="N9" s="59">
         <f t="shared" si="6"/>
-        <v>187603.05</v>
+        <v>293137.05</v>
       </c>
       <c r="O9" s="60">
         <f t="shared" si="2"/>
-        <v>193231.05</v>
+        <v>301931.05</v>
       </c>
       <c r="P9" s="34">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="122" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="123" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="123" t="s">
+      <c r="D10" s="123" t="s">
         <v>77</v>
-      </c>
-      <c r="D10" s="123" t="s">
-        <v>78</v>
       </c>
       <c r="E10" s="122">
         <v>6.97</v>
       </c>
       <c r="F10" s="53">
-        <v>97633.3</v>
-      </c>
-      <c r="G10" s="54"/>
+        <v>187638.06</v>
+      </c>
+      <c r="G10" s="54">
+        <v>97633</v>
+      </c>
       <c r="H10" s="55"/>
       <c r="I10" s="56">
         <f t="shared" si="4"/>
-        <v>97633.3</v>
+        <v>90005.06</v>
       </c>
       <c r="J10" s="56">
         <f t="shared" si="5"/>
-        <v>2880.1823500000005</v>
+        <v>2655.1492699999999</v>
       </c>
       <c r="K10" s="57">
         <f t="shared" si="0"/>
@@ -2979,11 +2993,11 @@
       </c>
       <c r="N10" s="59">
         <f t="shared" si="6"/>
-        <v>187638.06</v>
+        <v>179785.06</v>
       </c>
       <c r="O10" s="60">
         <f t="shared" si="2"/>
-        <v>193267.06</v>
+        <v>185179.06</v>
       </c>
       <c r="P10" s="34">
         <f t="shared" si="7"/>
@@ -2992,33 +3006,33 @@
       <c r="Q10" s="103"/>
       <c r="R10" s="102"/>
     </row>
-    <row r="11" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="122" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="122" t="s">
+      <c r="D11" s="122" t="s">
         <v>80</v>
-      </c>
-      <c r="D11" s="122" t="s">
-        <v>81</v>
       </c>
       <c r="E11" s="125">
         <v>6.75</v>
       </c>
       <c r="F11" s="53">
-        <v>73279.649999999994</v>
+        <v>84375.07</v>
       </c>
       <c r="G11" s="54">
-        <f>73280</f>
-        <v>73280</v>
+        <f>F11</f>
+        <v>84375.07</v>
       </c>
       <c r="H11" s="55"/>
       <c r="I11" s="56">
         <f t="shared" si="4"/>
-        <v>-0.35000000000582077</v>
+        <v>0</v>
       </c>
       <c r="J11" s="56">
         <f t="shared" si="5"/>
@@ -3048,31 +3062,31 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="122" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="122" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="122" t="s">
+      <c r="D12" s="122" t="s">
         <v>83</v>
-      </c>
-      <c r="D12" s="122" t="s">
-        <v>84</v>
       </c>
       <c r="E12" s="125">
         <v>7.79</v>
       </c>
       <c r="F12" s="53">
-        <v>84570.14</v>
+        <v>97375.08</v>
       </c>
       <c r="G12" s="54">
         <f>F12</f>
-        <v>84570.14</v>
+        <v>97375.08</v>
       </c>
       <c r="H12" s="55"/>
       <c r="I12" s="56">
@@ -3107,34 +3121,37 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="139" t="s">
+      <c r="B13" s="123" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="123" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="139" t="s">
+      <c r="D13" s="123" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="139" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="140">
+      <c r="E13" s="124">
         <v>7.62</v>
       </c>
-      <c r="F13" s="141">
-        <v>101571.58</v>
-      </c>
-      <c r="G13" s="141"/>
+      <c r="F13" s="54">
+        <v>199818.09</v>
+      </c>
+      <c r="G13" s="54">
+        <f>77374+119447.13+2997</f>
+        <v>199818.13</v>
+      </c>
       <c r="H13" s="55"/>
       <c r="I13" s="56">
         <f t="shared" si="4"/>
-        <v>101571.58</v>
+        <v>-4.0000000008149073E-2</v>
       </c>
       <c r="J13" s="56">
         <f t="shared" si="5"/>
-        <v>2996.3616100000004</v>
+        <v>0</v>
       </c>
       <c r="K13" s="57">
         <f t="shared" si="0"/>
@@ -3149,47 +3166,46 @@
       </c>
       <c r="N13" s="59">
         <f t="shared" si="6"/>
-        <v>199818.09</v>
+        <v>95250.09</v>
       </c>
       <c r="O13" s="60">
         <f t="shared" si="2"/>
-        <v>205813.09</v>
+        <v>98108.09</v>
       </c>
       <c r="P13" s="34">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
       <c r="Q13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="122" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="122" t="s">
-        <v>89</v>
-      </c>
       <c r="D14" s="122" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E14" s="125">
         <v>6.97</v>
       </c>
       <c r="F14" s="53">
-        <v>75668.02</v>
+        <v>87125.1</v>
       </c>
       <c r="G14" s="54">
-        <f t="shared" si="3"/>
-        <v>75668.02</v>
+        <v>89739.1</v>
       </c>
       <c r="H14" s="55"/>
       <c r="I14" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-2614</v>
       </c>
       <c r="J14" s="56">
         <f t="shared" si="5"/>
@@ -3208,45 +3224,48 @@
       </c>
       <c r="N14" s="59">
         <f t="shared" si="6"/>
-        <v>87125.1</v>
+        <v>84511.1</v>
       </c>
       <c r="O14" s="60">
         <f t="shared" si="2"/>
-        <v>89739.1</v>
+        <v>87046.1</v>
       </c>
       <c r="P14" s="34">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="122" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="122" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="122" t="s">
+      <c r="D15" s="122" t="s">
         <v>91</v>
-      </c>
-      <c r="D15" s="122" t="s">
-        <v>92</v>
       </c>
       <c r="E15" s="125">
         <v>14.01</v>
       </c>
       <c r="F15" s="53">
-        <v>403403.4</v>
-      </c>
-      <c r="G15" s="54"/>
+        <v>590429.11</v>
+      </c>
+      <c r="G15" s="54">
+        <f>380000+9612+185000+15817</f>
+        <v>590429</v>
+      </c>
       <c r="H15" s="55"/>
       <c r="I15" s="56">
         <f t="shared" si="4"/>
-        <v>403403.4</v>
+        <v>0.10999999998603016</v>
       </c>
       <c r="J15" s="56">
         <f t="shared" si="5"/>
-        <v>11900.400300000001</v>
+        <v>3.24499999958789E-3</v>
       </c>
       <c r="K15" s="57">
         <f t="shared" si="0"/>
@@ -3261,44 +3280,46 @@
       </c>
       <c r="N15" s="59">
         <f t="shared" si="6"/>
-        <v>590429.11</v>
+        <v>175125.11</v>
       </c>
       <c r="O15" s="60">
         <f t="shared" si="2"/>
-        <v>608142.11</v>
+        <v>180379.11</v>
       </c>
       <c r="P15" s="34">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="122" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="122" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="122" t="s">
+      <c r="D16" s="122" t="s">
         <v>94</v>
-      </c>
-      <c r="D16" s="122" t="s">
-        <v>95</v>
       </c>
       <c r="E16" s="125">
         <v>13.1</v>
       </c>
       <c r="F16" s="53">
-        <v>142216.79999999999</v>
+        <v>163750.12</v>
       </c>
       <c r="G16" s="54">
-        <f t="shared" si="3"/>
-        <v>142216.79999999999</v>
+        <v>168663.12</v>
       </c>
       <c r="H16" s="55"/>
       <c r="I16" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-4913</v>
       </c>
       <c r="J16" s="56">
         <f t="shared" si="5"/>
@@ -3317,21 +3338,21 @@
       </c>
       <c r="N16" s="59">
         <f t="shared" si="6"/>
-        <v>163750.12</v>
+        <v>158837.12</v>
       </c>
       <c r="O16" s="60">
         <f t="shared" si="2"/>
-        <v>168663.12</v>
+        <v>163602.12</v>
       </c>
       <c r="P16" s="34">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
       <c r="Q16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>16</v>
       </c>
@@ -3351,7 +3372,7 @@
       <c r="O17" s="60"/>
       <c r="P17" s="34"/>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="61"/>
       <c r="C18" s="62"/>
       <c r="D18" s="63"/>
@@ -3361,11 +3382,11 @@
       </c>
       <c r="F18" s="40">
         <f>SUM(F5:F17)</f>
-        <v>1662921.3099999998</v>
+        <v>2103802.7800000007</v>
       </c>
       <c r="G18" s="45">
         <f>SUM(G5:G17)</f>
-        <v>914085.10000000009</v>
+        <v>1685206.5899999999</v>
       </c>
       <c r="H18" s="45">
         <f>SUM(H5:H17)</f>
@@ -3387,105 +3408,98 @@
       </c>
       <c r="N18" s="65">
         <f>SUM(N5:N17)</f>
-        <v>2020929.7800000003</v>
+        <v>1681166.7800000003</v>
       </c>
       <c r="O18" s="65">
         <f>SUM(O5:O17)</f>
-        <v>2081557.7800000003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1731601.7800000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D19" s="38"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D20" s="159" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="159"/>
-      <c r="F20" s="159"/>
-      <c r="G20" s="159"/>
-      <c r="H20" s="159"/>
-      <c r="I20" s="159"/>
-      <c r="J20" s="159"/>
-      <c r="K20" s="159"/>
-      <c r="L20" s="159"/>
-      <c r="M20" s="159"/>
-      <c r="N20" s="159"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D21" s="159"/>
-      <c r="E21" s="159"/>
-      <c r="F21" s="159"/>
-      <c r="G21" s="159"/>
-      <c r="H21" s="159"/>
-      <c r="I21" s="159"/>
-      <c r="J21" s="159"/>
-      <c r="K21" s="159"/>
-      <c r="L21" s="159"/>
-      <c r="M21" s="159"/>
-      <c r="N21" s="159"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="159"/>
-      <c r="G22" s="159"/>
-      <c r="H22" s="159"/>
-      <c r="I22" s="159"/>
-      <c r="J22" s="159"/>
-      <c r="K22" s="159"/>
-      <c r="L22" s="159"/>
-      <c r="M22" s="159"/>
-      <c r="N22" s="159"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D23" s="159"/>
-      <c r="E23" s="159"/>
-      <c r="F23" s="159"/>
-      <c r="G23" s="159"/>
-      <c r="H23" s="159"/>
-      <c r="I23" s="159"/>
-      <c r="J23" s="159"/>
-      <c r="K23" s="159"/>
-      <c r="L23" s="159"/>
-      <c r="M23" s="159"/>
-      <c r="N23" s="159"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="159"/>
-      <c r="G24" s="159"/>
-      <c r="H24" s="159"/>
-      <c r="I24" s="159"/>
-      <c r="J24" s="159"/>
-      <c r="K24" s="159"/>
-      <c r="L24" s="159"/>
-      <c r="M24" s="159"/>
-      <c r="N24" s="159"/>
-    </row>
-    <row r="25" spans="1:16" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-      <c r="F25" s="159"/>
-      <c r="G25" s="159"/>
-      <c r="H25" s="159"/>
-      <c r="I25" s="159"/>
-      <c r="J25" s="159"/>
-      <c r="K25" s="159"/>
-      <c r="L25" s="159"/>
-      <c r="M25" s="159"/>
-      <c r="N25" s="159"/>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D20" s="169" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="169"/>
+      <c r="F20" s="169"/>
+      <c r="G20" s="169"/>
+      <c r="H20" s="169"/>
+      <c r="I20" s="169"/>
+      <c r="J20" s="169"/>
+      <c r="K20" s="169"/>
+      <c r="L20" s="169"/>
+      <c r="M20" s="169"/>
+      <c r="N20" s="169"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D21" s="169"/>
+      <c r="E21" s="169"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="169"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="169"/>
+      <c r="J21" s="169"/>
+      <c r="K21" s="169"/>
+      <c r="L21" s="169"/>
+      <c r="M21" s="169"/>
+      <c r="N21" s="169"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D22" s="169"/>
+      <c r="E22" s="169"/>
+      <c r="F22" s="169"/>
+      <c r="G22" s="169"/>
+      <c r="H22" s="169"/>
+      <c r="I22" s="169"/>
+      <c r="J22" s="169"/>
+      <c r="K22" s="169"/>
+      <c r="L22" s="169"/>
+      <c r="M22" s="169"/>
+      <c r="N22" s="169"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D23" s="169"/>
+      <c r="E23" s="169"/>
+      <c r="F23" s="169"/>
+      <c r="G23" s="169"/>
+      <c r="H23" s="169"/>
+      <c r="I23" s="169"/>
+      <c r="J23" s="169"/>
+      <c r="K23" s="169"/>
+      <c r="L23" s="169"/>
+      <c r="M23" s="169"/>
+      <c r="N23" s="169"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D24" s="169"/>
+      <c r="E24" s="169"/>
+      <c r="F24" s="169"/>
+      <c r="G24" s="169"/>
+      <c r="H24" s="169"/>
+      <c r="I24" s="169"/>
+      <c r="J24" s="169"/>
+      <c r="K24" s="169"/>
+      <c r="L24" s="169"/>
+      <c r="M24" s="169"/>
+      <c r="N24" s="169"/>
+    </row>
+    <row r="25" spans="1:16" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="169"/>
+      <c r="E25" s="169"/>
+      <c r="F25" s="169"/>
+      <c r="G25" s="169"/>
+      <c r="H25" s="169"/>
+      <c r="I25" s="169"/>
+      <c r="J25" s="169"/>
+      <c r="K25" s="169"/>
+      <c r="L25" s="169"/>
+      <c r="M25" s="169"/>
+      <c r="N25" s="169"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="B1:E2"/>
-    <mergeCell ref="F1:I2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="D20:N25"/>
     <mergeCell ref="H3:H4"/>
@@ -3497,6 +3511,13 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="B1:E2"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -3506,16 +3527,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E9F1C8-DABE-4F17-BF70-F15A1A832000}">
   <dimension ref="C4:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C4" s="142" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C7" s="146" t="s">
-        <v>132</v>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="139" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="140" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/2026/CABRERA/Febrero/Febrero CABRERA.xlsx
+++ b/2026/CABRERA/Febrero/Febrero CABRERA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\CABRERA\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\CABRERA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2881B9-4BBD-4272-9A9C-74FF9F32A4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C39D34-5D6B-4B72-B393-6767E245EE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$98</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -387,18 +382,12 @@
     <t>MEDIOS DE CONTACTOS: cabrera140rc@gmail.com  - INFORMAR CUALQUIER TIPO DE PAGO POR ALLI</t>
   </si>
   <si>
-    <t>el 2c abono 119447,13 el 20/01 - la pusimos no didentificada, este mes debe abonar $77.374,09</t>
-  </si>
-  <si>
     <t>Melisa Belmonte</t>
   </si>
   <si>
     <t xml:space="preserve">franco attolino </t>
   </si>
   <si>
-    <t>el 1B abono 80500 en enero - la pusimos no didentificada, este mes debe abonar $$92.551,04</t>
-  </si>
-  <si>
     <t>VTO 13/03</t>
   </si>
   <si>
@@ -436,6 +425,12 @@
   </si>
   <si>
     <t>PREVISION ORDINARIA - LIMPIEZA DE TANQUE</t>
+  </si>
+  <si>
+    <t>Silvia Marin De Sarni</t>
+  </si>
+  <si>
+    <t>Los depositos no identificados de meses anteriores de Silvia Sarni son del 1C</t>
   </si>
 </sst>
 </file>
@@ -624,7 +619,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -691,18 +686,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -1063,7 +1046,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1279,8 +1262,6 @@
     <xf numFmtId="44" fontId="0" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1309,6 +1290,45 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1351,45 +1371,11 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1458,9 +1444,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1498,9 +1484,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1533,26 +1519,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1585,26 +1554,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1779,20 +1731,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L98"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.28515625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.33203125" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="100" t="s">
         <v>50</v>
       </c>
@@ -1800,7 +1752,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="96" t="s">
         <v>104</v>
       </c>
@@ -1808,7 +1760,7 @@
       <c r="C2" s="96"/>
       <c r="D2" s="96"/>
     </row>
-    <row r="3" spans="1:8" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="96" t="s">
         <v>57</v>
       </c>
@@ -1816,44 +1768,44 @@
       <c r="C3" s="96"/>
       <c r="D3" s="96"/>
     </row>
-    <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="142" t="s">
+    <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="140" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="142"/>
+      <c r="B4" s="140"/>
       <c r="C4" s="97"/>
       <c r="D4" s="97"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="142"/>
-      <c r="B5" s="142"/>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="140"/>
+      <c r="B5" s="140"/>
       <c r="C5" s="97"/>
       <c r="D5" s="97"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="142"/>
-      <c r="B6" s="142"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="140"/>
+      <c r="B6" s="140"/>
       <c r="C6" s="97"/>
       <c r="D6" s="97"/>
     </row>
-    <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="142"/>
-      <c r="B7" s="142"/>
+    <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="140"/>
+      <c r="B7" s="140"/>
       <c r="C7" s="97"/>
       <c r="D7" s="97"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="150" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="150"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="150"/>
-    </row>
-    <row r="13" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="148" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="148"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="148"/>
+    </row>
+    <row r="13" spans="1:8" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F13" t="s">
         <v>101</v>
       </c>
@@ -1864,38 +1816,38 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="143" t="s">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="141" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="143"/>
-      <c r="C14" s="143"/>
-      <c r="D14" s="143"/>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="143"/>
-      <c r="B15" s="143"/>
-      <c r="C15" s="143"/>
-      <c r="D15" s="143"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="143"/>
-      <c r="B16" s="143"/>
-      <c r="C16" s="143"/>
-      <c r="D16" s="143"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="143"/>
-      <c r="B17" s="143"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="143"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="141"/>
+      <c r="C14" s="141"/>
+      <c r="D14" s="141"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="141"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="141"/>
+      <c r="B16" s="141"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="141"/>
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="141"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>15</v>
       </c>
@@ -1903,7 +1855,7 @@
       <c r="C21" s="8"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
         <v>40</v>
       </c>
@@ -1911,7 +1863,7 @@
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>106</v>
       </c>
@@ -1920,34 +1872,34 @@
         <v>395000</v>
       </c>
       <c r="D23" s="105" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="112"/>
       <c r="D24" s="99"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="112"/>
       <c r="D25" s="99"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="112"/>
       <c r="D26" s="99"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="113"/>
       <c r="D27" s="99"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="41" t="s">
         <v>41</v>
       </c>
@@ -1958,7 +1910,7 @@
       </c>
       <c r="D28" s="69"/>
     </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
         <v>0</v>
       </c>
@@ -1971,7 +1923,7 @@
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>26</v>
       </c>
@@ -1980,9 +1932,9 @@
       <c r="D30" s="71"/>
       <c r="F30" s="13"/>
     </row>
-    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="101" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B31" s="94"/>
       <c r="C31" s="132">
@@ -1991,7 +1943,7 @@
       <c r="D31" s="110"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
         <v>22</v>
       </c>
@@ -2002,7 +1954,7 @@
         <v>102000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>37</v>
       </c>
@@ -2010,17 +1962,17 @@
       <c r="C33" s="25"/>
       <c r="D33" s="50"/>
     </row>
-    <row r="34" spans="1:6" s="30" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="148" t="s">
+    <row r="34" spans="1:6" s="30" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="146" t="s">
         <v>95</v>
       </c>
-      <c r="B34" s="149"/>
+      <c r="B34" s="147"/>
       <c r="C34" s="134" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D34" s="109"/>
     </row>
-    <row r="35" spans="1:6" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="16" t="s">
         <v>1</v>
       </c>
@@ -2031,7 +1983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
         <v>23</v>
       </c>
@@ -2039,48 +1991,48 @@
       <c r="C36" s="28"/>
       <c r="D36" s="73"/>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C37" s="135"/>
       <c r="D37" s="109"/>
       <c r="F37" s="102"/>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C38" s="114"/>
       <c r="D38" s="109"/>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C39" s="114"/>
       <c r="D39" s="109"/>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C40" s="114"/>
       <c r="D40" s="108"/>
     </row>
-    <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="16" t="s">
         <v>2</v>
       </c>
@@ -2091,7 +2043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="23" t="s">
         <v>25</v>
       </c>
@@ -2099,7 +2051,7 @@
       <c r="C42" s="28"/>
       <c r="D42" s="73"/>
     </row>
-    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>97</v>
       </c>
@@ -2108,10 +2060,10 @@
         <v>84708.24</v>
       </c>
       <c r="D43" s="107" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>96</v>
       </c>
@@ -2120,10 +2072,10 @@
         <v>185724.36</v>
       </c>
       <c r="D44" s="105" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>105</v>
       </c>
@@ -2132,10 +2084,10 @@
         <v>259590</v>
       </c>
       <c r="D45" s="105" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="16" t="s">
         <v>3</v>
       </c>
@@ -2146,7 +2098,7 @@
         <v>530022.6</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="23" t="s">
         <v>24</v>
       </c>
@@ -2154,17 +2106,17 @@
       <c r="C47" s="27"/>
       <c r="D47" s="75"/>
     </row>
-    <row r="48" spans="1:6" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="126" t="s">
         <v>98</v>
       </c>
       <c r="B48" s="104"/>
       <c r="C48" s="114" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D48" s="105"/>
     </row>
-    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
         <v>8</v>
       </c>
@@ -2175,7 +2127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="23" t="s">
         <v>18</v>
       </c>
@@ -2183,7 +2135,7 @@
       <c r="C50" s="18"/>
       <c r="D50" s="75"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>100</v>
       </c>
@@ -2193,7 +2145,7 @@
       </c>
       <c r="D51" s="79"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>99</v>
       </c>
@@ -2204,7 +2156,7 @@
       </c>
       <c r="D52" s="77"/>
     </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="39" t="s">
         <v>22</v>
       </c>
@@ -2215,30 +2167,30 @@
         <v>96164.74</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="68"/>
       <c r="D54" s="81"/>
     </row>
-    <row r="55" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="144" t="s">
-        <v>133</v>
-      </c>
-      <c r="B55" s="145"/>
-      <c r="C55" s="146"/>
+    <row r="55" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="142" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="143"/>
+      <c r="C55" s="144"/>
       <c r="D55" s="82">
         <f>1350000-1123187.34</f>
         <v>226812.65999999992</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="C56" s="83"/>
       <c r="D56" s="84"/>
       <c r="E56" s="34"/>
     </row>
-    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>19</v>
       </c>
@@ -2251,16 +2203,16 @@
       <c r="E57" s="34"/>
       <c r="F57" s="34"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C58" s="83"/>
       <c r="D58" s="83"/>
       <c r="F58" s="103"/>
     </row>
-    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C59" s="83"/>
       <c r="D59" s="83"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>27</v>
       </c>
@@ -2268,25 +2220,25 @@
       <c r="C60" s="87"/>
       <c r="D60" s="88"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="148"/>
-      <c r="B61" s="149"/>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="146"/>
+      <c r="B61" s="147"/>
       <c r="C61" s="76"/>
       <c r="D61" s="74"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="148"/>
-      <c r="B62" s="149"/>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="146"/>
+      <c r="B62" s="147"/>
       <c r="C62" s="76"/>
       <c r="D62" s="74"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="91"/>
       <c r="B63" s="92"/>
       <c r="C63" s="76"/>
       <c r="D63" s="74"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="37"/>
       <c r="B64" s="36"/>
       <c r="C64" s="43"/>
@@ -2295,9 +2247,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="19" t="s">
         <v>28</v>
       </c>
@@ -2305,8 +2257,8 @@
       <c r="C67" s="20"/>
       <c r="D67" s="111"/>
     </row>
-    <row r="68" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="69" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>29</v>
       </c>
@@ -2317,8 +2269,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="71" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="66" t="s">
         <v>20</v>
       </c>
@@ -2328,7 +2280,7 @@
       </c>
       <c r="C71" s="34"/>
     </row>
-    <row r="72" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="66" t="s">
         <v>21</v>
       </c>
@@ -2337,7 +2289,7 @@
         <v>1123187.3400000001</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="66" t="s">
         <v>30</v>
       </c>
@@ -2346,7 +2298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="66" t="s">
         <v>45</v>
       </c>
@@ -2355,13 +2307,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="14" t="s">
         <v>39</v>
       </c>
       <c r="B78" s="31"/>
     </row>
-    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="127" t="s">
         <v>115</v>
       </c>
@@ -2370,7 +2322,7 @@
       </c>
       <c r="D79" s="34"/>
     </row>
-    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="128" t="s">
         <v>48</v>
       </c>
@@ -2379,7 +2331,7 @@
         <v>1685206.5899999999</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="128" t="s">
         <v>47</v>
       </c>
@@ -2388,7 +2340,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
         <v>55</v>
       </c>
@@ -2396,7 +2348,7 @@
         <v>-2372</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="15" t="s">
         <v>55</v>
       </c>
@@ -2404,7 +2356,7 @@
         <v>-2997</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="15" t="s">
         <v>55</v>
       </c>
@@ -2412,31 +2364,31 @@
         <v>-15817</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B85" s="106">
         <v>-119447.13</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B86" s="106">
         <v>-80500</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B87" s="106">
         <v>-185000</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="15" t="s">
         <v>31</v>
       </c>
@@ -2445,7 +2397,7 @@
         <v>-1123187.3400000001</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="15" t="s">
         <v>32</v>
       </c>
@@ -2454,7 +2406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="129" t="s">
         <v>8</v>
       </c>
@@ -2464,37 +2416,37 @@
       </c>
       <c r="D90" s="34"/>
     </row>
-    <row r="91" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="33"/>
       <c r="C91" s="34"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="147" t="s">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="145" t="s">
         <v>38</v>
       </c>
-      <c r="B93" s="147"/>
-    </row>
-    <row r="94" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="147"/>
-      <c r="B94" s="147"/>
-    </row>
-    <row r="95" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="145"/>
+    </row>
+    <row r="94" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="145"/>
+      <c r="B94" s="145"/>
+    </row>
+    <row r="95" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="89" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B95" s="26">
         <v>100000</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="89" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B96" s="26">
         <v>100000</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="35" t="s">
         <v>8</v>
       </c>
@@ -2503,7 +2455,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L98" s="7"/>
     </row>
   </sheetData>
@@ -2526,50 +2478,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" customWidth="1"/>
-    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" customWidth="1"/>
+    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="155" t="str">
+      <c r="B1" s="166" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco: Santander
 C.U.I.T.   30-71774143-5
 CBU: 0720533020000000956840 ALIAS: BLONDA.LAGO.CORO
 Nº de cuenta: 533-009568/4</v>
       </c>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="155" t="s">
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="166" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="151" t="s">
+      <c r="G1" s="167"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="162" t="s">
         <v>112</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="163"/>
       <c r="L1" s="136" t="s">
         <v>113</v>
       </c>
@@ -2580,18 +2532,18 @@
       <c r="O1" s="130"/>
       <c r="P1" s="13"/>
     </row>
-    <row r="2" spans="1:18" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="154"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="164"/>
+      <c r="K2" s="165"/>
       <c r="L2" s="137" t="s">
         <v>114</v>
       </c>
@@ -2599,75 +2551,75 @@
       <c r="N2" s="115"/>
       <c r="O2" s="131"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="161" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="172" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="163" t="s">
+      <c r="B3" s="174" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="165" t="s">
+      <c r="C3" s="152" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="165" t="s">
+      <c r="D3" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="165" t="s">
+      <c r="E3" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="165" t="s">
+      <c r="F3" s="152" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="165" t="s">
+      <c r="G3" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="165" t="s">
+      <c r="H3" s="152" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="173" t="s">
+      <c r="I3" s="157" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="171" t="s">
+      <c r="J3" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="171" t="s">
+      <c r="K3" s="154" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="171" t="s">
+      <c r="L3" s="154" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="176" t="s">
+      <c r="M3" s="160" t="s">
         <v>44</v>
       </c>
       <c r="N3" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="149" t="s">
         <v>42</v>
       </c>
       <c r="R3" s="34"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="162"/>
-      <c r="B4" s="164"/>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="170"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="170"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="172"/>
-      <c r="K4" s="175"/>
-      <c r="L4" s="172"/>
-      <c r="M4" s="177"/>
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="173"/>
+      <c r="B4" s="175"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="153"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="153"/>
+      <c r="I4" s="158"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="159"/>
+      <c r="L4" s="155"/>
+      <c r="M4" s="161"/>
       <c r="N4" s="44" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="O4" s="168"/>
-    </row>
-    <row r="5" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="150"/>
+    </row>
+    <row r="5" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
@@ -2720,7 +2672,7 @@
       </c>
       <c r="Q5" s="34"/>
     </row>
-    <row r="6" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -2740,7 +2692,7 @@
         <v>97375.02</v>
       </c>
       <c r="G6" s="54">
-        <f t="shared" ref="G6:G16" si="3">F6</f>
+        <f t="shared" ref="G6" si="3">F6</f>
         <v>97375.02</v>
       </c>
       <c r="H6" s="55"/>
@@ -2776,8 +2728,8 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="141" t="s">
+    <row r="7" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="139" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="123" t="s">
@@ -2836,7 +2788,7 @@
       </c>
       <c r="R7" s="34"/>
     </row>
-    <row r="8" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -2892,21 +2844,21 @@
         <v>0.04</v>
       </c>
       <c r="Q8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R8" s="34"/>
     </row>
-    <row r="9" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="122" t="s">
+      <c r="B9" s="177" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="122" t="s">
+      <c r="C9" s="177" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="122" t="s">
+      <c r="D9" s="177" t="s">
         <v>74</v>
       </c>
       <c r="E9" s="133">
@@ -2948,8 +2900,11 @@
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
@@ -3006,7 +2961,7 @@
       <c r="Q10" s="103"/>
       <c r="R10" s="102"/>
     </row>
-    <row r="11" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
@@ -3065,7 +3020,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -3121,7 +3076,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -3177,10 +3132,10 @@
         <v>0.09</v>
       </c>
       <c r="Q13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
@@ -3235,7 +3190,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
@@ -3291,10 +3246,10 @@
         <v>0.10999999999999999</v>
       </c>
       <c r="Q15" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
@@ -3352,7 +3307,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>16</v>
       </c>
@@ -3372,7 +3327,7 @@
       <c r="O17" s="60"/>
       <c r="P17" s="34"/>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="61"/>
       <c r="C18" s="62"/>
       <c r="D18" s="63"/>
@@ -3415,91 +3370,98 @@
         <v>1731601.7800000007</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D19" s="38"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D20" s="169" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D20" s="151" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="169"/>
-      <c r="F20" s="169"/>
-      <c r="G20" s="169"/>
-      <c r="H20" s="169"/>
-      <c r="I20" s="169"/>
-      <c r="J20" s="169"/>
-      <c r="K20" s="169"/>
-      <c r="L20" s="169"/>
-      <c r="M20" s="169"/>
-      <c r="N20" s="169"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D21" s="169"/>
-      <c r="E21" s="169"/>
-      <c r="F21" s="169"/>
-      <c r="G21" s="169"/>
-      <c r="H21" s="169"/>
-      <c r="I21" s="169"/>
-      <c r="J21" s="169"/>
-      <c r="K21" s="169"/>
-      <c r="L21" s="169"/>
-      <c r="M21" s="169"/>
-      <c r="N21" s="169"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D22" s="169"/>
-      <c r="E22" s="169"/>
-      <c r="F22" s="169"/>
-      <c r="G22" s="169"/>
-      <c r="H22" s="169"/>
-      <c r="I22" s="169"/>
-      <c r="J22" s="169"/>
-      <c r="K22" s="169"/>
-      <c r="L22" s="169"/>
-      <c r="M22" s="169"/>
-      <c r="N22" s="169"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D23" s="169"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="169"/>
-      <c r="G23" s="169"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="169"/>
-      <c r="J23" s="169"/>
-      <c r="K23" s="169"/>
-      <c r="L23" s="169"/>
-      <c r="M23" s="169"/>
-      <c r="N23" s="169"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D24" s="169"/>
-      <c r="E24" s="169"/>
-      <c r="F24" s="169"/>
-      <c r="G24" s="169"/>
-      <c r="H24" s="169"/>
-      <c r="I24" s="169"/>
-      <c r="J24" s="169"/>
-      <c r="K24" s="169"/>
-      <c r="L24" s="169"/>
-      <c r="M24" s="169"/>
-      <c r="N24" s="169"/>
-    </row>
-    <row r="25" spans="1:16" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="169"/>
-      <c r="E25" s="169"/>
-      <c r="F25" s="169"/>
-      <c r="G25" s="169"/>
-      <c r="H25" s="169"/>
-      <c r="I25" s="169"/>
-      <c r="J25" s="169"/>
-      <c r="K25" s="169"/>
-      <c r="L25" s="169"/>
-      <c r="M25" s="169"/>
-      <c r="N25" s="169"/>
+      <c r="E20" s="151"/>
+      <c r="F20" s="151"/>
+      <c r="G20" s="151"/>
+      <c r="H20" s="151"/>
+      <c r="I20" s="151"/>
+      <c r="J20" s="151"/>
+      <c r="K20" s="151"/>
+      <c r="L20" s="151"/>
+      <c r="M20" s="151"/>
+      <c r="N20" s="151"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D21" s="151"/>
+      <c r="E21" s="151"/>
+      <c r="F21" s="151"/>
+      <c r="G21" s="151"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D22" s="151"/>
+      <c r="E22" s="151"/>
+      <c r="F22" s="151"/>
+      <c r="G22" s="151"/>
+      <c r="H22" s="151"/>
+      <c r="I22" s="151"/>
+      <c r="J22" s="151"/>
+      <c r="K22" s="151"/>
+      <c r="L22" s="151"/>
+      <c r="M22" s="151"/>
+      <c r="N22" s="151"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D23" s="151"/>
+      <c r="E23" s="151"/>
+      <c r="F23" s="151"/>
+      <c r="G23" s="151"/>
+      <c r="H23" s="151"/>
+      <c r="I23" s="151"/>
+      <c r="J23" s="151"/>
+      <c r="K23" s="151"/>
+      <c r="L23" s="151"/>
+      <c r="M23" s="151"/>
+      <c r="N23" s="151"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="151"/>
+      <c r="H24" s="151"/>
+      <c r="I24" s="151"/>
+      <c r="J24" s="151"/>
+      <c r="K24" s="151"/>
+      <c r="L24" s="151"/>
+      <c r="M24" s="151"/>
+      <c r="N24" s="151"/>
+    </row>
+    <row r="25" spans="1:16" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="151"/>
+      <c r="E25" s="151"/>
+      <c r="F25" s="151"/>
+      <c r="G25" s="151"/>
+      <c r="H25" s="151"/>
+      <c r="I25" s="151"/>
+      <c r="J25" s="151"/>
+      <c r="K25" s="151"/>
+      <c r="L25" s="151"/>
+      <c r="M25" s="151"/>
+      <c r="N25" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="B1:E2"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="D20:N25"/>
     <mergeCell ref="H3:H4"/>
@@ -3511,13 +3473,6 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="B1:E2"/>
-    <mergeCell ref="F1:I2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -3526,17 +3481,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E9F1C8-DABE-4F17-BF70-F15A1A832000}">
-  <dimension ref="C4:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C4" s="139" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C7" s="140" t="s">
-        <v>120</v>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C4" s="178" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
